--- a/FINAL_SUBMISSION/03_股票候选池/03_候选股票池及初步分析表.xlsx
+++ b/FINAL_SUBMISSION/03_股票候选池/03_候选股票池及初步分析表.xlsx
@@ -528,18 +528,14 @@
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>33.35</t>
-        </is>
-      </c>
-      <c r="E2" s="2" t="n">
-        <v>13.11</v>
-      </c>
-      <c r="F2" s="2" t="n">
-        <v>4.59</v>
-      </c>
+          <t>33.86</t>
+        </is>
+      </c>
+      <c r="E2" s="2" t="n"/>
+      <c r="F2" s="2" t="n"/>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>综合评分78.0分（基本面100/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分80.0分（基本面100/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
@@ -549,7 +545,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格站上60日均线；RSI=52.7中性区</t>
+          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=59.4中性区</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -564,7 +560,7 @@
       </c>
       <c r="L2" s="2" t="inlineStr">
         <is>
-          <t>基本面100 / 技术面56.0 / 综合78.0</t>
+          <t>基本面100 / 技术面60.0 / 综合80.0</t>
         </is>
       </c>
     </row>
@@ -586,18 +582,14 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>58.24</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>6.62</v>
-      </c>
-      <c r="F3" s="2" t="n">
-        <v>1.04</v>
-      </c>
+          <t>55.70</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>综合评分71.0分（基本面82.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分72.0分（基本面82.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
@@ -607,7 +599,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.9超买区，短期回调风险</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.2中性区</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -622,7 +614,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>基本面82.0 / 技术面60.0 / 综合71.0</t>
+          <t>基本面82.0 / 技术面62.0 / 综合72.0</t>
         </is>
       </c>
     </row>
@@ -644,15 +636,11 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>28.42</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>19.21</v>
-      </c>
-      <c r="F4" s="2" t="n">
-        <v>3.22</v>
-      </c>
+          <t>27.87</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="n"/>
+      <c r="F4" s="2" t="n"/>
       <c r="G4" s="2" t="inlineStr">
         <is>
           <t>综合评分70.0分（基本面78.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -665,7 +653,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=59.7中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=39.0中性区</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -702,18 +690,18 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>351.00</t>
+          <t>335.49</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>19.11</v>
+        <v>18.26</v>
       </c>
       <c r="F5" s="2" t="n">
-        <v>4.36</v>
+        <v>4.16</v>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>综合评分69.0分（基本面87.0/技术面51.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -723,7 +711,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=15.6超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=14.7超卖区；近20日已跌-14.1%，接近超跌</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -738,55 +726,51 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>基本面87.0 / 技术面51.0 / 综合69.0</t>
+          <t>基本面87.0 / 技术面50.0 / 综合68.5</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>600519</t>
+          <t>600036</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>贵州茅台</t>
+          <t>招商银行</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>白酒</t>
+          <t>银行</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1330.00</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>20.42</v>
-      </c>
-      <c r="F6" s="2" t="n">
-        <v>6.62</v>
-      </c>
+          <t>40.90</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="n"/>
+      <c r="F6" s="2" t="n"/>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.5分（基本面73.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分67.0分（基本面72.0/技术面62.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。价格站上60日均线；MACD红柱放大；RSI=63.6中性区</t>
+          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=67.6中性区</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -796,50 +780,50 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>基本面73.0 / 技术面60.0 / 综合66.5</t>
+          <t>基本面72.0 / 技术面62.0 / 综合67.0</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>600036</t>
+          <t>000333</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>招商银行</t>
+          <t>美的集团</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>银行</t>
+          <t>家电</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>41.69</t>
+          <t>85.15</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>6.93</v>
+        <v>14.64</v>
       </c>
       <c r="F7" s="2" t="n">
-        <v>0.92</v>
+        <v>3.07</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>综合评分66.0分（基本面72.0/技术面60.0），技术面中期趋势向上，可关注/持有; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=6.71%，盈利能力一般；营收同比+4.83%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>中期趋势向上，可关注/持有。均线多头排列(5&gt;10&gt;20&gt;60)；MACD红柱放大；RSI=84.0超买区，短期回调风险</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=52.2中性区</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -854,55 +838,51 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>基本面72.0 / 技术面60.0 / 综合66.0</t>
+          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>000333</t>
+          <t>600519</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>美的集团</t>
+          <t>贵州茅台</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>家电</t>
+          <t>白酒</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>87.57</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>15.05</v>
-      </c>
-      <c r="F8" s="2" t="n">
-        <v>3.15</v>
-      </c>
+          <t>1309.30</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="n"/>
+      <c r="F8" s="2" t="n"/>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
+          <t>综合评分64.5分（基本面73.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>基本面优秀，具备中长期配置价值；加权ROE=11.33%，盈利能力良好；营收同比+3.46%，保持正增长</t>
+          <t>基本面优秀，具备中长期配置价值；加权ROE=16.75%（≥15%），盈利能力优秀，长期股东回报有保障；营收同比+1.30%，保持正增长</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。均线多头排列(5&gt;10&gt;20&gt;60)；RSI=75.7超买区，短期回调风险</t>
+          <t>趋势中性，观望。价格站上60日均线；RSI=50.5中性区</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
+          <t>归母净利润同比-1.95%，利润下滑需警惕；宏观与行业景气度波动风险；财务数据为历史披露数据，存在业绩变脸可能</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -912,7 +892,7 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>基本面75.0 / 技术面56.0 / 综合65.5</t>
+          <t>基本面73.0 / 技术面56.0 / 综合64.5</t>
         </is>
       </c>
     </row>
@@ -949,7 +929,7 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>综合评分53.5分（基本面60.0/技术面47.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
+          <t>综合评分53.0分（基本面60.0/技术面46.0），技术面趋势中性，观望; 基本面判断: 指数型ETF，跟踪指数成分整体基本面，个股财务风险分散</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
@@ -959,7 +939,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；RSI=27.0超卖区</t>
+          <t>趋势中性，观望。价格位于60日均线下方，中期趋势偏弱；MACD红柱放大；RSI=44.7中性区</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -974,7 +954,7 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>基本面60.0 / 技术面47.0 / 综合53.5</t>
+          <t>基本面60.0 / 技术面46.0 / 综合53.0</t>
         </is>
       </c>
     </row>

--- a/FINAL_SUBMISSION/03_股票候选池/03_候选股票池及初步分析表.xlsx
+++ b/FINAL_SUBMISSION/03_股票候选池/03_候选股票池及初步分析表.xlsx
@@ -693,12 +693,8 @@
           <t>335.49</t>
         </is>
       </c>
-      <c r="E5" s="2" t="n">
-        <v>18.26</v>
-      </c>
-      <c r="F5" s="2" t="n">
-        <v>4.16</v>
-      </c>
+      <c r="E5" s="2" t="n"/>
+      <c r="F5" s="2" t="n"/>
       <c r="G5" s="2" t="inlineStr">
         <is>
           <t>综合评分68.5分（基本面87.0/技术面50.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
@@ -805,12 +801,8 @@
           <t>85.15</t>
         </is>
       </c>
-      <c r="E7" s="2" t="n">
-        <v>14.64</v>
-      </c>
-      <c r="F7" s="2" t="n">
-        <v>3.07</v>
-      </c>
+      <c r="E7" s="2" t="n"/>
+      <c r="F7" s="2" t="n"/>
       <c r="G7" s="2" t="inlineStr">
         <is>
           <t>综合评分65.5分（基本面75.0/技术面56.0），技术面趋势中性，观望; 基本面判断: 基本面优秀，具备中长期配置价值</t>
